--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2931" uniqueCount="319">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -538,6 +538,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -727,6 +730,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -737,10 +743,25 @@
     <t>Bloc narratif de la section</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -753,6 +774,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -760,6 +790,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -767,6 +800,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -920,6 +956,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1296,7 +1338,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4953,7 +4995,9 @@
       <c r="K36" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L36" s="2"/>
+      <c r="L36" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5024,10 +5068,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5061,7 +5105,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>74</v>
@@ -5083,7 +5127,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5101,7 +5145,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5121,10 +5165,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5158,7 +5202,7 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>74</v>
@@ -5180,7 +5224,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5198,7 +5242,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5218,10 +5262,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5235,7 +5279,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5247,10 +5291,10 @@
         <v>95</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5301,7 +5345,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5321,10 +5365,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5338,7 +5382,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5347,13 +5391,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5404,7 +5448,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5424,10 +5468,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5525,10 +5569,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5544,7 +5588,7 @@
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5557,7 +5601,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5569,7 +5613,7 @@
         <v>74</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>74</v>
@@ -5608,7 +5652,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5628,17 +5672,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>75</v>
@@ -5647,7 +5691,7 @@
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5660,7 +5704,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5672,7 +5716,7 @@
         <v>74</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>74</v>
@@ -5711,7 +5755,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5731,17 +5775,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5763,7 +5807,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5775,7 +5819,7 @@
         <v>74</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>74</v>
@@ -5814,7 +5858,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5834,17 +5878,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5866,7 +5910,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5917,7 +5961,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5937,17 +5981,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>75</v>
@@ -5956,7 +6000,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -5969,7 +6013,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5981,7 +6025,7 @@
         <v>74</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>74</v>
@@ -6020,7 +6064,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6040,10 +6084,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6066,11 +6110,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6121,7 +6165,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6141,10 +6185,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6171,7 +6215,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6222,7 +6266,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6242,17 +6286,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6270,11 +6314,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6325,7 +6369,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6345,17 +6389,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6373,11 +6417,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6428,7 +6472,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6448,17 +6492,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6476,11 +6520,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6531,7 +6575,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6551,10 +6595,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6568,7 +6612,7 @@
         <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>74</v>
@@ -6577,16 +6621,18 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6634,7 +6680,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6654,10 +6700,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6671,7 +6717,7 @@
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6680,15 +6726,17 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>74</v>
@@ -6737,7 +6785,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6757,10 +6805,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6783,12 +6831,16 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L54" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>74</v>
       </c>
@@ -6836,7 +6888,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6856,10 +6908,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6884,10 +6936,14 @@
       <c r="K55" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L55" s="2"/>
+      <c r="L55" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>74</v>
       </c>
@@ -6915,7 +6971,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -6933,7 +6989,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6953,10 +7009,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6979,12 +7035,18 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="L56" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="N56" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>74</v>
       </c>
@@ -7032,7 +7094,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7052,10 +7114,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7078,12 +7140,14 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>74</v>
       </c>
@@ -7131,7 +7195,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7151,10 +7215,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7177,12 +7241,14 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>74</v>
       </c>
@@ -7230,7 +7296,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7250,10 +7316,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7267,7 +7333,7 @@
         <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7276,10 +7342,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -7331,7 +7397,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7351,10 +7417,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7452,10 +7518,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7553,10 +7619,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7654,10 +7720,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7755,10 +7821,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7858,10 +7924,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7961,10 +8027,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8064,10 +8130,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8167,10 +8233,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8268,10 +8334,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8301,7 +8367,7 @@
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
@@ -8327,7 +8393,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>74</v>
@@ -8345,7 +8411,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8365,10 +8431,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8402,7 +8468,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>74</v>
@@ -8444,7 +8510,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8464,10 +8530,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8490,7 +8556,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8543,7 +8609,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8563,10 +8629,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8589,7 +8655,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8642,7 +8708,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8662,10 +8728,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8688,7 +8754,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8741,7 +8807,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8761,10 +8827,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8787,7 +8853,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8840,7 +8906,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8860,10 +8926,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8886,7 +8952,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8939,7 +9005,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8959,10 +9025,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8985,7 +9051,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9038,7 +9104,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9058,10 +9124,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9084,7 +9150,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9137,7 +9203,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9157,10 +9223,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9183,7 +9249,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9236,7 +9302,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9256,10 +9322,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9282,7 +9348,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9335,7 +9401,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9355,10 +9421,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9381,12 +9447,16 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="L80" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>74</v>
       </c>
@@ -9434,7 +9504,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9454,10 +9524,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9555,10 +9625,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9656,10 +9726,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9757,10 +9827,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9858,10 +9928,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9961,10 +10031,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10064,10 +10134,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10167,10 +10237,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10270,10 +10340,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10371,10 +10441,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10401,7 +10471,7 @@
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10410,7 +10480,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>74</v>
@@ -10452,7 +10522,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10472,10 +10542,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10509,7 +10579,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>74</v>
@@ -10551,7 +10621,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10571,10 +10641,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10597,7 +10667,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10650,7 +10720,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
